--- a/formlar/16. Organik Üretim/EMS.OR.FRM.21.04. Organik Kütle Dengesi Kayıt Formu.xlsx
+++ b/formlar/16. Organik Üretim/EMS.OR.FRM.21.04. Organik Kütle Dengesi Kayıt Formu.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Form" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +69,37 @@
       <name val="Calibri"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +121,18 @@
         <fgColor rgb="00F6F7F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00006600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF1DE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -184,11 +223,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <top style="medium"/>
+    </border>
+    <border>
+      <top style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+    </border>
+    <border/>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -247,6 +327,47 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -324,32 +445,67 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
-      <colOff>0</colOff>
+      <colOff>238124</colOff>
       <row>0</row>
-      <rowOff>0</rowOff>
+      <rowOff>198193</rowOff>
     </from>
-    <ext cx="1219200" cy="952500"/>
+    <to>
+      <col>2</col>
+      <colOff>171449</colOff>
+      <row>3</row>
+      <rowOff>205802</rowOff>
+    </to>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>15</col>
+      <colOff>66676</colOff>
+      <row>0</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>16</col>
+      <colOff>609600</colOff>
+      <row>3</row>
+      <rowOff>283176</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -668,327 +824,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="A1" s="26" t="n"/>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="28" t="n"/>
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>ORGANIC MASS BALANCE RECORD
 سجل موازنة الكتلة العضوية</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
+      <c r="H1" s="27" t="n"/>
+      <c r="I1" s="27" t="n"/>
+      <c r="J1" s="27" t="n"/>
+      <c r="K1" s="27" t="n"/>
+      <c r="L1" s="27" t="n"/>
+      <c r="M1" s="27" t="n"/>
+      <c r="N1" s="27" t="n"/>
+      <c r="O1" s="27" t="n"/>
+      <c r="P1" s="27" t="n"/>
+      <c r="Q1" s="27" t="n"/>
+      <c r="R1" s="30" t="inlineStr">
         <is>
           <t>DATE / التاريخ</t>
         </is>
       </c>
-      <c r="S1" s="5" t="n"/>
-      <c r="T1" s="6" t="inlineStr">
+      <c r="S1" s="31" t="n"/>
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>….../….../.…</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-      <c r="O2" s="1" t="n"/>
-      <c r="P2" s="1" t="n"/>
-      <c r="Q2" s="1" t="n"/>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="A2" s="33" t="n"/>
+      <c r="B2" s="34" t="n"/>
+      <c r="C2" s="34" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
+      <c r="F2" s="34" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="34" t="n"/>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="34" t="n"/>
+      <c r="K2" s="34" t="n"/>
+      <c r="L2" s="34" t="n"/>
+      <c r="M2" s="34" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="34" t="n"/>
+      <c r="P2" s="34" t="n"/>
+      <c r="Q2" s="34" t="n"/>
+      <c r="R2" s="30" t="inlineStr">
         <is>
           <t>FORM NUMBER / رقم النموذج</t>
         </is>
       </c>
-      <c r="S2" s="5" t="n"/>
-      <c r="T2" s="9" t="inlineStr">
+      <c r="S2" s="31" t="n"/>
+      <c r="T2" s="35" t="inlineStr">
         <is>
           <t>EMS.OR.FRM.21.04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
-      <c r="N3" s="1" t="n"/>
-      <c r="O3" s="1" t="n"/>
-      <c r="P3" s="1" t="n"/>
-      <c r="Q3" s="1" t="n"/>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="A3" s="33" t="n"/>
+      <c r="B3" s="34" t="n"/>
+      <c r="C3" s="34" t="n"/>
+      <c r="D3" s="34" t="n"/>
+      <c r="E3" s="34" t="n"/>
+      <c r="F3" s="34" t="n"/>
+      <c r="G3" s="34" t="n"/>
+      <c r="H3" s="34" t="n"/>
+      <c r="I3" s="34" t="n"/>
+      <c r="J3" s="34" t="n"/>
+      <c r="K3" s="34" t="n"/>
+      <c r="L3" s="34" t="n"/>
+      <c r="M3" s="34" t="n"/>
+      <c r="N3" s="34" t="n"/>
+      <c r="O3" s="34" t="n"/>
+      <c r="P3" s="34" t="n"/>
+      <c r="Q3" s="34" t="n"/>
+      <c r="R3" s="30" t="inlineStr">
         <is>
           <t>REVISION / المراجعة</t>
         </is>
       </c>
-      <c r="S3" s="5" t="n"/>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="S3" s="31" t="n"/>
+      <c r="T3" s="32" t="inlineStr">
         <is>
           <t>R00</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
-      <c r="Q4" s="1" t="n"/>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="A4" s="33" t="n"/>
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="34" t="n"/>
+      <c r="D4" s="34" t="n"/>
+      <c r="E4" s="34" t="n"/>
+      <c r="F4" s="34" t="n"/>
+      <c r="G4" s="34" t="n"/>
+      <c r="H4" s="34" t="n"/>
+      <c r="I4" s="34" t="n"/>
+      <c r="J4" s="34" t="n"/>
+      <c r="K4" s="34" t="n"/>
+      <c r="L4" s="34" t="n"/>
+      <c r="M4" s="34" t="n"/>
+      <c r="N4" s="34" t="n"/>
+      <c r="O4" s="34" t="n"/>
+      <c r="P4" s="34" t="n"/>
+      <c r="Q4" s="34" t="n"/>
+      <c r="R4" s="30" t="inlineStr">
         <is>
           <t>PUBLIC. DATE / تاريخ النشر</t>
         </is>
       </c>
-      <c r="S4" s="5" t="n"/>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="S4" s="31" t="n"/>
+      <c r="T4" s="32" t="inlineStr">
         <is>
           <t>19.10.2026</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>GENERAL INFORMATION / المعلومات العامة</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="37" t="n"/>
+      <c r="H6" s="37" t="n"/>
+      <c r="I6" s="37" t="n"/>
+      <c r="J6" s="37" t="n"/>
+      <c r="K6" s="37" t="n"/>
+      <c r="L6" s="37" t="n"/>
+      <c r="M6" s="37" t="n"/>
+      <c r="N6" s="37" t="n"/>
+      <c r="O6" s="37" t="n"/>
+      <c r="P6" s="37" t="n"/>
+      <c r="Q6" s="37" t="n"/>
+      <c r="R6" s="37" t="n"/>
+      <c r="S6" s="37" t="n"/>
+      <c r="T6" s="38" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Period / Order No
 الفترة / رقم الطلب</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="B7" s="37" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="inlineStr">
         <is>
           <t>Customer
 العميل</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="15" t="n"/>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="H7" s="37" t="n"/>
+      <c r="I7" s="37" t="n"/>
+      <c r="J7" s="37" t="n"/>
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="39" t="inlineStr">
         <is>
           <t>Standard  ☐ GOTS  ☐ OCS
 المعيار</t>
         </is>
       </c>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="15" t="n"/>
-      <c r="Q7" s="14" t="inlineStr">
+      <c r="M7" s="37" t="n"/>
+      <c r="N7" s="37" t="n"/>
+      <c r="O7" s="37" t="n"/>
+      <c r="P7" s="38" t="n"/>
+      <c r="Q7" s="39" t="inlineStr">
         <is>
           <t>Conversion factor
 معامل التحويل</t>
         </is>
       </c>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="15" t="n"/>
-      <c r="T7" s="15" t="n"/>
+      <c r="R7" s="37" t="n"/>
+      <c r="S7" s="37" t="n"/>
+      <c r="T7" s="38" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Product / material
 المنتج / المادة</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="37" t="n"/>
+      <c r="H8" s="37" t="n"/>
+      <c r="I8" s="37" t="n"/>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="39" t="inlineStr">
         <is>
           <t>Prepared by
 المعد</t>
         </is>
       </c>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="14" t="inlineStr">
+      <c r="L8" s="37" t="n"/>
+      <c r="M8" s="37" t="n"/>
+      <c r="N8" s="37" t="n"/>
+      <c r="O8" s="38" t="n"/>
+      <c r="P8" s="39" t="inlineStr">
         <is>
           <t>Date
 التاريخ</t>
         </is>
       </c>
-      <c r="Q8" s="15" t="n"/>
-      <c r="R8" s="15" t="n"/>
-      <c r="S8" s="15" t="n"/>
-      <c r="T8" s="15" t="n"/>
-    </row>
+      <c r="Q8" s="37" t="n"/>
+      <c r="R8" s="37" t="n"/>
+      <c r="S8" s="37" t="n"/>
+      <c r="T8" s="38" t="n"/>
+    </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>VOLUME RECONCILIATION BY STAGE / موازنة الكميات حسب المرحلة</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="37" t="n"/>
+      <c r="H10" s="37" t="n"/>
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="37" t="n"/>
+      <c r="K10" s="37" t="n"/>
+      <c r="L10" s="37" t="n"/>
+      <c r="M10" s="37" t="n"/>
+      <c r="N10" s="37" t="n"/>
+      <c r="O10" s="37" t="n"/>
+      <c r="P10" s="37" t="n"/>
+      <c r="Q10" s="37" t="n"/>
+      <c r="R10" s="37" t="n"/>
+      <c r="S10" s="37" t="n"/>
+      <c r="T10" s="38" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Stage
 المرحلة</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>Input Qty
 المدخلات</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>Output Qty
 المخرجات</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="40" t="inlineStr">
         <is>
           <t>Waste / Offcuts
 الفاقد / القصاصات</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="40" t="inlineStr">
         <is>
           <t>Rejects
 المرفوضات</t>
         </is>
       </c>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="40" t="inlineStr">
         <is>
           <t>Unit
 الوحدة</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="M11" s="40" t="inlineStr">
         <is>
           <t>Difference
 الفرق</t>
         </is>
       </c>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="N11" s="38" t="n"/>
+      <c r="O11" s="40" t="inlineStr">
         <is>
           <t>Diff %
 النسبة %</t>
         </is>
       </c>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="16" t="inlineStr">
+      <c r="P11" s="38" t="n"/>
+      <c r="Q11" s="40" t="inlineStr">
         <is>
           <t>Remarks
 ملاحظات</t>
         </is>
       </c>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
+      <c r="R11" s="37" t="n"/>
+      <c r="S11" s="37" t="n"/>
+      <c r="T11" s="38" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
@@ -996,31 +1154,31 @@
           <t>Certified input (TC)</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="38" t="n"/>
       <c r="D12" s="17" t="n"/>
-      <c r="E12" s="1" t="n"/>
+      <c r="E12" s="38" t="n"/>
       <c r="F12" s="17" t="n"/>
-      <c r="G12" s="1" t="n"/>
+      <c r="G12" s="38" t="n"/>
       <c r="H12" s="17" t="n"/>
-      <c r="I12" s="1" t="n"/>
+      <c r="I12" s="38" t="n"/>
       <c r="J12" s="17" t="n"/>
-      <c r="K12" s="1" t="n"/>
+      <c r="K12" s="38" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="17">
         <f>IF(D12="","",D12-F12-H12-J12)</f>
         <v/>
       </c>
-      <c r="N12" s="1" t="n"/>
+      <c r="N12" s="38" t="n"/>
       <c r="O12" s="18">
         <f>IF(OR(D12="",D12=0),"",M12/D12)</f>
         <v/>
       </c>
-      <c r="P12" s="1" t="n"/>
+      <c r="P12" s="38" t="n"/>
       <c r="Q12" s="17" t="n"/>
-      <c r="R12" s="1" t="n"/>
-      <c r="S12" s="1" t="n"/>
-      <c r="T12" s="1" t="n"/>
+      <c r="R12" s="37" t="n"/>
+      <c r="S12" s="37" t="n"/>
+      <c r="T12" s="38" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
@@ -1028,31 +1186,31 @@
           <t>Knitting</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="38" t="n"/>
       <c r="D13" s="17" t="n"/>
-      <c r="E13" s="1" t="n"/>
+      <c r="E13" s="38" t="n"/>
       <c r="F13" s="17" t="n"/>
-      <c r="G13" s="1" t="n"/>
+      <c r="G13" s="38" t="n"/>
       <c r="H13" s="17" t="n"/>
-      <c r="I13" s="1" t="n"/>
+      <c r="I13" s="38" t="n"/>
       <c r="J13" s="17" t="n"/>
-      <c r="K13" s="1" t="n"/>
+      <c r="K13" s="38" t="n"/>
       <c r="L13" s="17" t="n"/>
       <c r="M13" s="17">
         <f>IF(D13="","",D13-F13-H13-J13)</f>
         <v/>
       </c>
-      <c r="N13" s="1" t="n"/>
+      <c r="N13" s="38" t="n"/>
       <c r="O13" s="18">
         <f>IF(OR(D13="",D13=0),"",M13/D13)</f>
         <v/>
       </c>
-      <c r="P13" s="1" t="n"/>
+      <c r="P13" s="38" t="n"/>
       <c r="Q13" s="17" t="n"/>
-      <c r="R13" s="1" t="n"/>
-      <c r="S13" s="1" t="n"/>
-      <c r="T13" s="1" t="n"/>
+      <c r="R13" s="37" t="n"/>
+      <c r="S13" s="37" t="n"/>
+      <c r="T13" s="38" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
@@ -1060,31 +1218,31 @@
           <t>Dyeing and finishing</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="38" t="n"/>
       <c r="D14" s="17" t="n"/>
-      <c r="E14" s="1" t="n"/>
+      <c r="E14" s="38" t="n"/>
       <c r="F14" s="17" t="n"/>
-      <c r="G14" s="1" t="n"/>
+      <c r="G14" s="38" t="n"/>
       <c r="H14" s="17" t="n"/>
-      <c r="I14" s="1" t="n"/>
+      <c r="I14" s="38" t="n"/>
       <c r="J14" s="17" t="n"/>
-      <c r="K14" s="1" t="n"/>
+      <c r="K14" s="38" t="n"/>
       <c r="L14" s="17" t="n"/>
       <c r="M14" s="17">
         <f>IF(D14="","",D14-F14-H14-J14)</f>
         <v/>
       </c>
-      <c r="N14" s="1" t="n"/>
+      <c r="N14" s="38" t="n"/>
       <c r="O14" s="18">
         <f>IF(OR(D14="",D14=0),"",M14/D14)</f>
         <v/>
       </c>
-      <c r="P14" s="1" t="n"/>
+      <c r="P14" s="38" t="n"/>
       <c r="Q14" s="17" t="n"/>
-      <c r="R14" s="1" t="n"/>
-      <c r="S14" s="1" t="n"/>
-      <c r="T14" s="1" t="n"/>
+      <c r="R14" s="37" t="n"/>
+      <c r="S14" s="37" t="n"/>
+      <c r="T14" s="38" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
@@ -1092,31 +1250,31 @@
           <t>Cutting</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="38" t="n"/>
       <c r="D15" s="17" t="n"/>
-      <c r="E15" s="1" t="n"/>
+      <c r="E15" s="38" t="n"/>
       <c r="F15" s="17" t="n"/>
-      <c r="G15" s="1" t="n"/>
+      <c r="G15" s="38" t="n"/>
       <c r="H15" s="17" t="n"/>
-      <c r="I15" s="1" t="n"/>
+      <c r="I15" s="38" t="n"/>
       <c r="J15" s="17" t="n"/>
-      <c r="K15" s="1" t="n"/>
+      <c r="K15" s="38" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="17">
         <f>IF(D15="","",D15-F15-H15-J15)</f>
         <v/>
       </c>
-      <c r="N15" s="1" t="n"/>
+      <c r="N15" s="38" t="n"/>
       <c r="O15" s="18">
         <f>IF(OR(D15="",D15=0),"",M15/D15)</f>
         <v/>
       </c>
-      <c r="P15" s="1" t="n"/>
+      <c r="P15" s="38" t="n"/>
       <c r="Q15" s="17" t="n"/>
-      <c r="R15" s="1" t="n"/>
-      <c r="S15" s="1" t="n"/>
-      <c r="T15" s="1" t="n"/>
+      <c r="R15" s="37" t="n"/>
+      <c r="S15" s="37" t="n"/>
+      <c r="T15" s="38" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
@@ -1124,31 +1282,31 @@
           <t>Sewing</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="38" t="n"/>
       <c r="D16" s="17" t="n"/>
-      <c r="E16" s="1" t="n"/>
+      <c r="E16" s="38" t="n"/>
       <c r="F16" s="17" t="n"/>
-      <c r="G16" s="1" t="n"/>
+      <c r="G16" s="38" t="n"/>
       <c r="H16" s="17" t="n"/>
-      <c r="I16" s="1" t="n"/>
+      <c r="I16" s="38" t="n"/>
       <c r="J16" s="17" t="n"/>
-      <c r="K16" s="1" t="n"/>
+      <c r="K16" s="38" t="n"/>
       <c r="L16" s="17" t="n"/>
       <c r="M16" s="17">
         <f>IF(D16="","",D16-F16-H16-J16)</f>
         <v/>
       </c>
-      <c r="N16" s="1" t="n"/>
+      <c r="N16" s="38" t="n"/>
       <c r="O16" s="18">
         <f>IF(OR(D16="",D16=0),"",M16/D16)</f>
         <v/>
       </c>
-      <c r="P16" s="1" t="n"/>
+      <c r="P16" s="38" t="n"/>
       <c r="Q16" s="17" t="n"/>
-      <c r="R16" s="1" t="n"/>
-      <c r="S16" s="1" t="n"/>
-      <c r="T16" s="1" t="n"/>
+      <c r="R16" s="37" t="n"/>
+      <c r="S16" s="37" t="n"/>
+      <c r="T16" s="38" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
@@ -1156,139 +1314,140 @@
           <t>Packing / shipment</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="38" t="n"/>
       <c r="D17" s="17" t="n"/>
-      <c r="E17" s="1" t="n"/>
+      <c r="E17" s="38" t="n"/>
       <c r="F17" s="17" t="n"/>
-      <c r="G17" s="1" t="n"/>
+      <c r="G17" s="38" t="n"/>
       <c r="H17" s="17" t="n"/>
-      <c r="I17" s="1" t="n"/>
+      <c r="I17" s="38" t="n"/>
       <c r="J17" s="17" t="n"/>
-      <c r="K17" s="1" t="n"/>
+      <c r="K17" s="38" t="n"/>
       <c r="L17" s="17" t="n"/>
       <c r="M17" s="17">
         <f>IF(D17="","",D17-F17-H17-J17)</f>
         <v/>
       </c>
-      <c r="N17" s="1" t="n"/>
+      <c r="N17" s="38" t="n"/>
       <c r="O17" s="18">
         <f>IF(OR(D17="",D17=0),"",M17/D17)</f>
         <v/>
       </c>
-      <c r="P17" s="1" t="n"/>
+      <c r="P17" s="38" t="n"/>
       <c r="Q17" s="17" t="n"/>
-      <c r="R17" s="1" t="n"/>
-      <c r="S17" s="1" t="n"/>
-      <c r="T17" s="1" t="n"/>
-    </row>
+      <c r="R17" s="37" t="n"/>
+      <c r="S17" s="37" t="n"/>
+      <c r="T17" s="38" t="n"/>
+    </row>
+    <row r="18"/>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>RESULT / النتيجة</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="13" t="n"/>
-      <c r="S19" s="13" t="n"/>
-      <c r="T19" s="13" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="37" t="n"/>
+      <c r="H19" s="37" t="n"/>
+      <c r="I19" s="37" t="n"/>
+      <c r="J19" s="37" t="n"/>
+      <c r="K19" s="37" t="n"/>
+      <c r="L19" s="37" t="n"/>
+      <c r="M19" s="37" t="n"/>
+      <c r="N19" s="37" t="n"/>
+      <c r="O19" s="37" t="n"/>
+      <c r="P19" s="37" t="n"/>
+      <c r="Q19" s="37" t="n"/>
+      <c r="R19" s="37" t="n"/>
+      <c r="S19" s="37" t="n"/>
+      <c r="T19" s="38" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>Certified organic input total
 إجمالي المدخلات العضوية المعتمدة</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="39" t="inlineStr">
         <is>
           <t>Certified output + documented losses
 المخرجات المعتمدة + الفاقد الموثق</t>
         </is>
       </c>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="14" t="inlineStr">
+      <c r="I20" s="37" t="n"/>
+      <c r="J20" s="37" t="n"/>
+      <c r="K20" s="37" t="n"/>
+      <c r="L20" s="37" t="n"/>
+      <c r="M20" s="37" t="n"/>
+      <c r="N20" s="38" t="n"/>
+      <c r="O20" s="39" t="inlineStr">
         <is>
           <t>Organic quantity claimed
 الكمية المُدّعى أنها عضوية</t>
         </is>
       </c>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="15" t="n"/>
-      <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="n"/>
-      <c r="T20" s="15" t="n"/>
+      <c r="P20" s="37" t="n"/>
+      <c r="Q20" s="37" t="n"/>
+      <c r="R20" s="37" t="n"/>
+      <c r="S20" s="37" t="n"/>
+      <c r="T20" s="38" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>Check item / بند الفحص</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="16" t="inlineStr">
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="37" t="n"/>
+      <c r="H21" s="37" t="n"/>
+      <c r="I21" s="37" t="n"/>
+      <c r="J21" s="37" t="n"/>
+      <c r="K21" s="37" t="n"/>
+      <c r="L21" s="37" t="n"/>
+      <c r="M21" s="37" t="n"/>
+      <c r="N21" s="38" t="n"/>
+      <c r="O21" s="40" t="inlineStr">
         <is>
           <t>Yes
 نعم</t>
         </is>
       </c>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="16" t="inlineStr">
+      <c r="P21" s="38" t="n"/>
+      <c r="Q21" s="40" t="inlineStr">
         <is>
           <t>No
 لا</t>
         </is>
       </c>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="16" t="inlineStr">
+      <c r="R21" s="38" t="n"/>
+      <c r="S21" s="40" t="inlineStr">
         <is>
           <t>N/A
 لا ينطبق</t>
         </is>
       </c>
-      <c r="T21" s="5" t="n"/>
+      <c r="T21" s="38" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="20" t="n">
@@ -1300,36 +1459,36 @@
 المخرجات المُدّعى أنها عضوية لا تتجاوز المدخلات المعتمدة مطروحًا منها فاقد العمليات.</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n"/>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n"/>
-      <c r="F22" s="1" t="n"/>
-      <c r="G22" s="1" t="n"/>
-      <c r="H22" s="1" t="n"/>
-      <c r="I22" s="1" t="n"/>
-      <c r="J22" s="1" t="n"/>
-      <c r="K22" s="1" t="n"/>
-      <c r="L22" s="1" t="n"/>
-      <c r="M22" s="1" t="n"/>
-      <c r="N22" s="1" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="37" t="n"/>
+      <c r="I22" s="37" t="n"/>
+      <c r="J22" s="37" t="n"/>
+      <c r="K22" s="37" t="n"/>
+      <c r="L22" s="37" t="n"/>
+      <c r="M22" s="37" t="n"/>
+      <c r="N22" s="38" t="n"/>
       <c r="O22" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P22" s="1" t="n"/>
+      <c r="P22" s="38" t="n"/>
       <c r="Q22" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R22" s="1" t="n"/>
+      <c r="R22" s="38" t="n"/>
       <c r="S22" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T22" s="1" t="n"/>
+      <c r="T22" s="38" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="20" t="n">
@@ -1341,36 +1500,36 @@
 الفرق غير المبرر أقل من حد التنبيه الداخلي 2% من المدخلات.</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n"/>
-      <c r="D23" s="1" t="n"/>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="n"/>
-      <c r="L23" s="1" t="n"/>
-      <c r="M23" s="1" t="n"/>
-      <c r="N23" s="1" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="37" t="n"/>
+      <c r="H23" s="37" t="n"/>
+      <c r="I23" s="37" t="n"/>
+      <c r="J23" s="37" t="n"/>
+      <c r="K23" s="37" t="n"/>
+      <c r="L23" s="37" t="n"/>
+      <c r="M23" s="37" t="n"/>
+      <c r="N23" s="38" t="n"/>
       <c r="O23" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P23" s="1" t="n"/>
+      <c r="P23" s="38" t="n"/>
       <c r="Q23" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R23" s="1" t="n"/>
+      <c r="R23" s="38" t="n"/>
       <c r="S23" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T23" s="1" t="n"/>
+      <c r="T23" s="38" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="20" t="n">
@@ -1382,62 +1541,63 @@
 تم التحقيق في الفرق وإبلاغ جهة الاعتماد (إن لم يُفسَّر).</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="1" t="n"/>
-      <c r="F24" s="1" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="1" t="n"/>
-      <c r="I24" s="1" t="n"/>
-      <c r="J24" s="1" t="n"/>
-      <c r="K24" s="1" t="n"/>
-      <c r="L24" s="1" t="n"/>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="1" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="37" t="n"/>
+      <c r="H24" s="37" t="n"/>
+      <c r="I24" s="37" t="n"/>
+      <c r="J24" s="37" t="n"/>
+      <c r="K24" s="37" t="n"/>
+      <c r="L24" s="37" t="n"/>
+      <c r="M24" s="37" t="n"/>
+      <c r="N24" s="38" t="n"/>
       <c r="O24" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P24" s="1" t="n"/>
+      <c r="P24" s="38" t="n"/>
       <c r="Q24" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R24" s="1" t="n"/>
+      <c r="R24" s="38" t="n"/>
       <c r="S24" s="22" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T24" s="1" t="n"/>
-    </row>
+      <c r="T24" s="38" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>NOTES / ملاحظات</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="13" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="13" t="n"/>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="13" t="n"/>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="37" t="n"/>
+      <c r="H26" s="37" t="n"/>
+      <c r="I26" s="37" t="n"/>
+      <c r="J26" s="37" t="n"/>
+      <c r="K26" s="37" t="n"/>
+      <c r="L26" s="37" t="n"/>
+      <c r="M26" s="37" t="n"/>
+      <c r="N26" s="37" t="n"/>
+      <c r="O26" s="37" t="n"/>
+      <c r="P26" s="37" t="n"/>
+      <c r="Q26" s="37" t="n"/>
+      <c r="R26" s="37" t="n"/>
+      <c r="S26" s="37" t="n"/>
+      <c r="T26" s="38" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
@@ -1445,81 +1605,82 @@
           <t>Explanation of differences, conversion factors used.</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n"/>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
-      <c r="F27" s="1" t="n"/>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="n"/>
-      <c r="K27" s="1" t="n"/>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="1" t="n"/>
-      <c r="O27" s="1" t="n"/>
-      <c r="P27" s="1" t="n"/>
-      <c r="Q27" s="1" t="n"/>
-      <c r="R27" s="1" t="n"/>
-      <c r="S27" s="1" t="n"/>
-      <c r="T27" s="1" t="n"/>
+      <c r="B27" s="42" t="n"/>
+      <c r="C27" s="42" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="42" t="n"/>
+      <c r="G27" s="42" t="n"/>
+      <c r="H27" s="42" t="n"/>
+      <c r="I27" s="42" t="n"/>
+      <c r="J27" s="42" t="n"/>
+      <c r="K27" s="42" t="n"/>
+      <c r="L27" s="42" t="n"/>
+      <c r="M27" s="42" t="n"/>
+      <c r="N27" s="42" t="n"/>
+      <c r="O27" s="42" t="n"/>
+      <c r="P27" s="42" t="n"/>
+      <c r="Q27" s="42" t="n"/>
+      <c r="R27" s="42" t="n"/>
+      <c r="S27" s="42" t="n"/>
+      <c r="T27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n"/>
-      <c r="B28" s="1" t="n"/>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
-      <c r="E28" s="1" t="n"/>
-      <c r="F28" s="1" t="n"/>
-      <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="n"/>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="1" t="n"/>
-      <c r="K28" s="1" t="n"/>
-      <c r="L28" s="1" t="n"/>
-      <c r="M28" s="1" t="n"/>
-      <c r="N28" s="1" t="n"/>
-      <c r="O28" s="1" t="n"/>
-      <c r="P28" s="1" t="n"/>
-      <c r="Q28" s="1" t="n"/>
-      <c r="R28" s="1" t="n"/>
-      <c r="S28" s="1" t="n"/>
-      <c r="T28" s="1" t="n"/>
-    </row>
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="43" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="n"/>
+      <c r="H28" s="43" t="n"/>
+      <c r="I28" s="43" t="n"/>
+      <c r="J28" s="43" t="n"/>
+      <c r="K28" s="43" t="n"/>
+      <c r="L28" s="43" t="n"/>
+      <c r="M28" s="43" t="n"/>
+      <c r="N28" s="43" t="n"/>
+      <c r="O28" s="43" t="n"/>
+      <c r="P28" s="43" t="n"/>
+      <c r="Q28" s="43" t="n"/>
+      <c r="R28" s="43" t="n"/>
+      <c r="S28" s="43" t="n"/>
+      <c r="T28" s="11" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>Production Planning / تخطيط الإنتاج</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="B30" s="45" t="n"/>
+      <c r="C30" s="45" t="n"/>
+      <c r="D30" s="45" t="n"/>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="46" t="n"/>
+      <c r="H30" s="44" t="inlineStr">
         <is>
           <t>OCS / GOTS Coordinator / منسق OCS / GOTS</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="16" t="inlineStr">
+      <c r="I30" s="45" t="n"/>
+      <c r="J30" s="45" t="n"/>
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="45" t="n"/>
+      <c r="N30" s="46" t="n"/>
+      <c r="O30" s="44" t="inlineStr">
         <is>
           <t>Quality / الجودة</t>
         </is>
       </c>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="5" t="n"/>
-      <c r="T30" s="5" t="n"/>
+      <c r="P30" s="45" t="n"/>
+      <c r="Q30" s="45" t="n"/>
+      <c r="R30" s="45" t="n"/>
+      <c r="S30" s="45" t="n"/>
+      <c r="T30" s="46" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
@@ -1527,106 +1688,93 @@
           <t>Name - Signature - Date / الاسم - التوقيع - التاريخ</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="1" t="n"/>
-      <c r="D31" s="1" t="n"/>
-      <c r="E31" s="1" t="n"/>
-      <c r="F31" s="1" t="n"/>
-      <c r="G31" s="1" t="n"/>
+      <c r="B31" s="42" t="n"/>
+      <c r="C31" s="42" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="42" t="n"/>
+      <c r="G31" s="2" t="n"/>
       <c r="H31" s="24" t="inlineStr">
         <is>
           <t>Name - Signature - Date / الاسم - التوقيع - التاريخ</t>
         </is>
       </c>
-      <c r="I31" s="1" t="n"/>
-      <c r="J31" s="1" t="n"/>
-      <c r="K31" s="1" t="n"/>
-      <c r="L31" s="1" t="n"/>
-      <c r="M31" s="1" t="n"/>
-      <c r="N31" s="1" t="n"/>
+      <c r="I31" s="42" t="n"/>
+      <c r="J31" s="42" t="n"/>
+      <c r="K31" s="42" t="n"/>
+      <c r="L31" s="42" t="n"/>
+      <c r="M31" s="42" t="n"/>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="24" t="inlineStr">
         <is>
           <t>Name - Signature - Date / الاسم - التوقيع - التاريخ</t>
         </is>
       </c>
-      <c r="P31" s="1" t="n"/>
-      <c r="Q31" s="1" t="n"/>
-      <c r="R31" s="1" t="n"/>
-      <c r="S31" s="1" t="n"/>
-      <c r="T31" s="1" t="n"/>
+      <c r="P31" s="42" t="n"/>
+      <c r="Q31" s="42" t="n"/>
+      <c r="R31" s="42" t="n"/>
+      <c r="S31" s="42" t="n"/>
+      <c r="T31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="n"/>
-      <c r="C32" s="1" t="n"/>
-      <c r="D32" s="1" t="n"/>
-      <c r="E32" s="1" t="n"/>
-      <c r="F32" s="1" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
-      <c r="I32" s="1" t="n"/>
-      <c r="J32" s="1" t="n"/>
-      <c r="K32" s="1" t="n"/>
-      <c r="L32" s="1" t="n"/>
-      <c r="M32" s="1" t="n"/>
-      <c r="N32" s="1" t="n"/>
-      <c r="O32" s="1" t="n"/>
-      <c r="P32" s="1" t="n"/>
-      <c r="Q32" s="1" t="n"/>
-      <c r="R32" s="1" t="n"/>
-      <c r="S32" s="1" t="n"/>
-      <c r="T32" s="1" t="n"/>
+      <c r="A32" s="7" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="7" t="n"/>
+      <c r="T32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="1" t="n"/>
-      <c r="C33" s="1" t="n"/>
-      <c r="D33" s="1" t="n"/>
-      <c r="E33" s="1" t="n"/>
-      <c r="F33" s="1" t="n"/>
-      <c r="G33" s="1" t="n"/>
-      <c r="H33" s="1" t="n"/>
-      <c r="I33" s="1" t="n"/>
-      <c r="J33" s="1" t="n"/>
-      <c r="K33" s="1" t="n"/>
-      <c r="L33" s="1" t="n"/>
-      <c r="M33" s="1" t="n"/>
-      <c r="N33" s="1" t="n"/>
-      <c r="O33" s="1" t="n"/>
-      <c r="P33" s="1" t="n"/>
-      <c r="Q33" s="1" t="n"/>
-      <c r="R33" s="1" t="n"/>
-      <c r="S33" s="1" t="n"/>
-      <c r="T33" s="1" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="43" t="n"/>
+      <c r="E33" s="43" t="n"/>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="43" t="n"/>
+      <c r="J33" s="43" t="n"/>
+      <c r="K33" s="43" t="n"/>
+      <c r="L33" s="43" t="n"/>
+      <c r="M33" s="43" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="43" t="n"/>
+      <c r="Q33" s="43" t="n"/>
+      <c r="R33" s="43" t="n"/>
+      <c r="S33" s="43" t="n"/>
+      <c r="T33" s="11" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>Retention: at least 5 years or per certification body / customer requirement. Any nonconformity opens a corrective action (DÖF). | الاحتفاظ: 5 سنوات على الأقل أو حسب متطلبات جهة الاعتماد / العميل. وتفتح أي حالة عدم مطابقة إجراءً تصحيحيًا (DÖF).</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n"/>
-      <c r="C35" s="1" t="n"/>
-      <c r="D35" s="1" t="n"/>
-      <c r="E35" s="1" t="n"/>
-      <c r="F35" s="1" t="n"/>
-      <c r="G35" s="1" t="n"/>
-      <c r="H35" s="1" t="n"/>
-      <c r="I35" s="1" t="n"/>
-      <c r="J35" s="1" t="n"/>
-      <c r="K35" s="1" t="n"/>
-      <c r="L35" s="1" t="n"/>
-      <c r="M35" s="1" t="n"/>
-      <c r="N35" s="1" t="n"/>
-      <c r="O35" s="1" t="n"/>
-      <c r="P35" s="1" t="n"/>
-      <c r="Q35" s="1" t="n"/>
-      <c r="R35" s="1" t="n"/>
-      <c r="S35" s="1" t="n"/>
-      <c r="T35" s="1" t="n"/>
+      <c r="B35" s="45" t="n"/>
+      <c r="C35" s="45" t="n"/>
+      <c r="D35" s="45" t="n"/>
+      <c r="E35" s="45" t="n"/>
+      <c r="F35" s="45" t="n"/>
+      <c r="G35" s="45" t="n"/>
+      <c r="H35" s="45" t="n"/>
+      <c r="I35" s="45" t="n"/>
+      <c r="J35" s="45" t="n"/>
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="45" t="n"/>
+      <c r="M35" s="45" t="n"/>
+      <c r="N35" s="45" t="n"/>
+      <c r="O35" s="45" t="n"/>
+      <c r="P35" s="45" t="n"/>
+      <c r="Q35" s="45" t="n"/>
+      <c r="R35" s="45" t="n"/>
+      <c r="S35" s="45" t="n"/>
+      <c r="T35" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="100">
     <mergeCell ref="Q21:R21"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="L7:P7"/>
@@ -1652,10 +1800,10 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="S22:T22"/>
-    <mergeCell ref="C1:Q1"/>
     <mergeCell ref="Q17:T17"/>
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D1:O4"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="Q23:R23"/>
@@ -1691,12 +1839,10 @@
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="J16:K16"/>
-    <mergeCell ref="C1:Q4"/>
     <mergeCell ref="Q14:T14"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="H31:N33"/>
     <mergeCell ref="O23:P23"/>
-    <mergeCell ref="A1:B4"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="O30:T30"/>

--- a/formlar/16. Organik Üretim/EMS.OR.FRM.21.04. Organik Kütle Dengesi Kayıt Formu.xlsx
+++ b/formlar/16. Organik Üretim/EMS.OR.FRM.21.04. Organik Kütle Dengesi Kayıt Formu.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,12 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -132,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -264,11 +270,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -368,6 +402,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,6 +511,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -502,6 +544,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -827,23 +872,24 @@
       <c r="A1" s="26" t="n"/>
       <c r="B1" s="27" t="n"/>
       <c r="C1" s="28" t="n"/>
-      <c r="D1" s="29" t="inlineStr">
-        <is>
-          <t>ORGANIC MASS BALANCE RECORD
+      <c r="D1" s="47" t="inlineStr">
+        <is>
+          <t>ORGANİK KÜTLE DENGESİ KAYDI
+ORGANIC MASS BALANCE RECORD
 سجل موازنة الكتلة العضوية</t>
         </is>
       </c>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="27" t="n"/>
+      <c r="E1" s="48" t="n"/>
+      <c r="F1" s="48" t="n"/>
+      <c r="G1" s="48" t="n"/>
+      <c r="H1" s="48" t="n"/>
+      <c r="I1" s="48" t="n"/>
+      <c r="J1" s="48" t="n"/>
+      <c r="K1" s="48" t="n"/>
+      <c r="L1" s="48" t="n"/>
+      <c r="M1" s="48" t="n"/>
+      <c r="N1" s="48" t="n"/>
+      <c r="O1" s="48" t="n"/>
       <c r="P1" s="27" t="n"/>
       <c r="Q1" s="27" t="n"/>
       <c r="R1" s="30" t="inlineStr">
@@ -851,7 +897,7 @@
           <t>DATE / التاريخ</t>
         </is>
       </c>
-      <c r="S1" s="31" t="n"/>
+      <c r="S1" s="49" t="n"/>
       <c r="T1" s="32" t="inlineStr">
         <is>
           <t>….../….../.…</t>
@@ -862,18 +908,6 @@
       <c r="A2" s="33" t="n"/>
       <c r="B2" s="34" t="n"/>
       <c r="C2" s="34" t="n"/>
-      <c r="D2" s="34" t="n"/>
-      <c r="E2" s="34" t="n"/>
-      <c r="F2" s="34" t="n"/>
-      <c r="G2" s="34" t="n"/>
-      <c r="H2" s="34" t="n"/>
-      <c r="I2" s="34" t="n"/>
-      <c r="J2" s="34" t="n"/>
-      <c r="K2" s="34" t="n"/>
-      <c r="L2" s="34" t="n"/>
-      <c r="M2" s="34" t="n"/>
-      <c r="N2" s="34" t="n"/>
-      <c r="O2" s="34" t="n"/>
       <c r="P2" s="34" t="n"/>
       <c r="Q2" s="34" t="n"/>
       <c r="R2" s="30" t="inlineStr">
@@ -881,7 +915,7 @@
           <t>FORM NUMBER / رقم النموذج</t>
         </is>
       </c>
-      <c r="S2" s="31" t="n"/>
+      <c r="S2" s="49" t="n"/>
       <c r="T2" s="35" t="inlineStr">
         <is>
           <t>EMS.OR.FRM.21.04</t>
@@ -892,18 +926,6 @@
       <c r="A3" s="33" t="n"/>
       <c r="B3" s="34" t="n"/>
       <c r="C3" s="34" t="n"/>
-      <c r="D3" s="34" t="n"/>
-      <c r="E3" s="34" t="n"/>
-      <c r="F3" s="34" t="n"/>
-      <c r="G3" s="34" t="n"/>
-      <c r="H3" s="34" t="n"/>
-      <c r="I3" s="34" t="n"/>
-      <c r="J3" s="34" t="n"/>
-      <c r="K3" s="34" t="n"/>
-      <c r="L3" s="34" t="n"/>
-      <c r="M3" s="34" t="n"/>
-      <c r="N3" s="34" t="n"/>
-      <c r="O3" s="34" t="n"/>
       <c r="P3" s="34" t="n"/>
       <c r="Q3" s="34" t="n"/>
       <c r="R3" s="30" t="inlineStr">
@@ -911,7 +933,7 @@
           <t>REVISION / المراجعة</t>
         </is>
       </c>
-      <c r="S3" s="31" t="n"/>
+      <c r="S3" s="49" t="n"/>
       <c r="T3" s="32" t="inlineStr">
         <is>
           <t>R00</t>
@@ -922,18 +944,6 @@
       <c r="A4" s="33" t="n"/>
       <c r="B4" s="34" t="n"/>
       <c r="C4" s="34" t="n"/>
-      <c r="D4" s="34" t="n"/>
-      <c r="E4" s="34" t="n"/>
-      <c r="F4" s="34" t="n"/>
-      <c r="G4" s="34" t="n"/>
-      <c r="H4" s="34" t="n"/>
-      <c r="I4" s="34" t="n"/>
-      <c r="J4" s="34" t="n"/>
-      <c r="K4" s="34" t="n"/>
-      <c r="L4" s="34" t="n"/>
-      <c r="M4" s="34" t="n"/>
-      <c r="N4" s="34" t="n"/>
-      <c r="O4" s="34" t="n"/>
       <c r="P4" s="34" t="n"/>
       <c r="Q4" s="34" t="n"/>
       <c r="R4" s="30" t="inlineStr">
@@ -941,14 +951,13 @@
           <t>PUBLIC. DATE / تاريخ النشر</t>
         </is>
       </c>
-      <c r="S4" s="31" t="n"/>
+      <c r="S4" s="49" t="n"/>
       <c r="T4" s="32" t="inlineStr">
         <is>
           <t>19.10.2026</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="36" t="inlineStr">
         <is>
@@ -1054,7 +1063,6 @@
       <c r="S8" s="37" t="n"/>
       <c r="T8" s="38" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
         <is>
@@ -1340,7 +1348,6 @@
       <c r="S17" s="37" t="n"/>
       <c r="T17" s="38" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="36" t="inlineStr">
         <is>
@@ -1572,7 +1579,6 @@
       </c>
       <c r="T24" s="38" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="36" t="inlineStr">
         <is>
@@ -1647,40 +1653,39 @@
       <c r="S28" s="43" t="n"/>
       <c r="T28" s="11" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
           <t>Production Planning / تخطيط الإنتاج</t>
         </is>
       </c>
-      <c r="B30" s="45" t="n"/>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
-      <c r="G30" s="46" t="n"/>
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="37" t="n"/>
+      <c r="G30" s="38" t="n"/>
       <c r="H30" s="44" t="inlineStr">
         <is>
           <t>OCS / GOTS Coordinator / منسق OCS / GOTS</t>
         </is>
       </c>
-      <c r="I30" s="45" t="n"/>
-      <c r="J30" s="45" t="n"/>
-      <c r="K30" s="45" t="n"/>
-      <c r="L30" s="45" t="n"/>
-      <c r="M30" s="45" t="n"/>
-      <c r="N30" s="46" t="n"/>
+      <c r="I30" s="37" t="n"/>
+      <c r="J30" s="37" t="n"/>
+      <c r="K30" s="37" t="n"/>
+      <c r="L30" s="37" t="n"/>
+      <c r="M30" s="37" t="n"/>
+      <c r="N30" s="38" t="n"/>
       <c r="O30" s="44" t="inlineStr">
         <is>
           <t>Quality / الجودة</t>
         </is>
       </c>
-      <c r="P30" s="45" t="n"/>
-      <c r="Q30" s="45" t="n"/>
-      <c r="R30" s="45" t="n"/>
-      <c r="S30" s="45" t="n"/>
-      <c r="T30" s="46" t="n"/>
+      <c r="P30" s="37" t="n"/>
+      <c r="Q30" s="37" t="n"/>
+      <c r="R30" s="37" t="n"/>
+      <c r="S30" s="37" t="n"/>
+      <c r="T30" s="38" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
@@ -1746,32 +1751,31 @@
       <c r="S33" s="43" t="n"/>
       <c r="T33" s="11" t="n"/>
     </row>
-    <row r="34"/>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="36" t="inlineStr">
         <is>
           <t>Retention: at least 5 years or per certification body / customer requirement. Any nonconformity opens a corrective action (DÖF). | الاحتفاظ: 5 سنوات على الأقل أو حسب متطلبات جهة الاعتماد / العميل. وتفتح أي حالة عدم مطابقة إجراءً تصحيحيًا (DÖF).</t>
         </is>
       </c>
-      <c r="B35" s="45" t="n"/>
-      <c r="C35" s="45" t="n"/>
-      <c r="D35" s="45" t="n"/>
-      <c r="E35" s="45" t="n"/>
-      <c r="F35" s="45" t="n"/>
-      <c r="G35" s="45" t="n"/>
-      <c r="H35" s="45" t="n"/>
-      <c r="I35" s="45" t="n"/>
-      <c r="J35" s="45" t="n"/>
-      <c r="K35" s="45" t="n"/>
-      <c r="L35" s="45" t="n"/>
-      <c r="M35" s="45" t="n"/>
-      <c r="N35" s="45" t="n"/>
-      <c r="O35" s="45" t="n"/>
-      <c r="P35" s="45" t="n"/>
-      <c r="Q35" s="45" t="n"/>
-      <c r="R35" s="45" t="n"/>
-      <c r="S35" s="45" t="n"/>
-      <c r="T35" s="46" t="n"/>
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="37" t="n"/>
+      <c r="G35" s="37" t="n"/>
+      <c r="H35" s="37" t="n"/>
+      <c r="I35" s="37" t="n"/>
+      <c r="J35" s="37" t="n"/>
+      <c r="K35" s="37" t="n"/>
+      <c r="L35" s="37" t="n"/>
+      <c r="M35" s="37" t="n"/>
+      <c r="N35" s="37" t="n"/>
+      <c r="O35" s="37" t="n"/>
+      <c r="P35" s="37" t="n"/>
+      <c r="Q35" s="37" t="n"/>
+      <c r="R35" s="37" t="n"/>
+      <c r="S35" s="37" t="n"/>
+      <c r="T35" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="100">
